--- a/光伏配储项目/电价数据/2026/仙源站.xlsx
+++ b/光伏配储项目/电价数据/2026/仙源站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50979</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.69074</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5628300000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.49445</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.44135</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.43567</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43793</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45475</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43934</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42328</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40895</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40219</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41297</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41737</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42077</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41433</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44432</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26084</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.19437</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.24576</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.06719</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.05585</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.03912</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.01774</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.03896</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03801</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.03374</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.01722</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08531</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.02253</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.01727</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00158</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.1446</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21255</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23513</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.18338</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.09135</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.03352</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01039</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.09779</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11432</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.15852</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.21091</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.14437</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.12232</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.10501</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.16981</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.19195</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.16031</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.42484</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.42719</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.51888</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.4585</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.72304</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.60868</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.48788</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.46156</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>-0.04118</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.55447</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.52513</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.1678</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.48111</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.48626</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.5824199999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.54003</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.42387</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47881</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41129</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42031</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6086</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.40132</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7402799999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.95275</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.79959</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5372</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52407</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5066700000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50351</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50251</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47443</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38147</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42304</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.51693</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6298400000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7221799999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43758</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.43533</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.07636</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.25179</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.26006</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.26484</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.22115</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.57902</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.03675</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.26887</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.25635</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.28258</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.28803</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.22753</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.55508</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.04213</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.27077</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.28796</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.21488</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.15399</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.21775</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.22042</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23047</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.24963</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.3936</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.21351</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.20498</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68604</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.79471</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.78703</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.18937</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8028099999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.7513099999999999</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.27627</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.4354</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.59023</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43882</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43306</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40678</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33294</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51573</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.46766</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43256</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44867</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39261</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47404</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44831</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44269</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39559</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28277</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27849</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.12481</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.27273</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.24714</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.28072</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.22891</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.38899</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.24446</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.27908</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.19845</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.12584</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.18584</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.17459</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24182</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29195</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27949</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.25343</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.25416</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.20371</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.15848</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.26477</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.4514</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.48264</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.28375</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.27919</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.24787</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.25892</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.29534</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34341</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.28804</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.29992</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4705</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26304</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.20224</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.12156</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11451</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08517</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.26473</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.22612</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.11216</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28518</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.44011</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.19204</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06376</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.25495</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.20246</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.03764</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.02842</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.25755</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.01279</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.02913</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.05647</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.09298000000000001</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.25005</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.19328</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.22223</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.18046</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.22989</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16079</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.23422</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.25085</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.28939</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.26131</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.28856</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41978</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.48397</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.40814</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.39413</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.27698</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28798</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29104</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28367</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.29968</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28283</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.2863</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26052</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04017</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04532</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.03994</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.03979</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04296</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04614</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04452</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04654999999999999</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04211</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04653</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04616</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04455</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04469</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.0457</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04464</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04599</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04918</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04506</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04579</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04722999999999999</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04713000000000001</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04505</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04697</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22031</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04728</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05119</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00256</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03691</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09845000000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38282</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41203</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35139</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66362</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4466</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10242</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04247</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04627000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04576</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04531</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04532</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04531</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04454</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04255</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03196</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04134</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10655</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03765</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04706</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04206</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04217</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04206</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04436</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04427</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04426</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04202</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04146</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04397</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04127</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03979</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04428</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04183</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04286</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04047</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04374</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04683</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04671</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2015</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14408</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27049</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33702</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32087</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28974</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27272</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27271</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28257</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17364</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17247</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14896</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16068</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15999</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23843</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21541</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22795</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27111</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28756</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28262</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28235</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.26944</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28239</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.26751</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.40701</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.40385</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15735</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2815299999999999</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50747</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79111</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6218899999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49776</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78083</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.91995</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49424</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9233300000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.89295</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31158</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.91592</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6362599999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.21496</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88244</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.56623</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.35951</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.05255</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.55962</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.81556</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53084</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.79767</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.79713</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87981</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8867699999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.51623</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.42119</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.42954</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4763</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.23664</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8796799999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5515399999999999</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.65124</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54565</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50614</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42771</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44233</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45133</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45306</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42152</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39289</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.4342200000000001</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39114</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41021</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45114</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58872</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42842</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59662</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60157</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6555599999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45172</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.40513</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5552999999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44642</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.86207</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6616599999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8291000000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.81212</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8472499999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43256</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.41818</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27122</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45288</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35338</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9883200000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4878</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.45259</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.54714</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.61541</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.40331</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.46062</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.41401</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40052</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50073</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.2778</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16457</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28124</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29681</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26084</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20056</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.25755</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27502</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27544</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43182</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.27637</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44774</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59782</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88967</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35077</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14035</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70747</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.80027</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65228</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5877599999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43997</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43773</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5010899999999999</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43414</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41328</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42845</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42355</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43455</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42398</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39636</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40282</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5628500000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.06619</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.50591</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.04044</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.67276</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.21947</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.54898</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26574</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26604</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.29723</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26575</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28939</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.38385</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37263</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.43915</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.40657</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5870700000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46452</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.71447</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46585</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4387200000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42465</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32572</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42474</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39298</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.25968</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26807</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23589</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14733</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29646</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15419</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14439</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14085</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14418</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14265</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25745</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14472</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26717</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14218</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.03493</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11417</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11328</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14546</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14153</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14671</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28742</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45084</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.4007</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39324</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44091</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44108</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44047</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44542</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44487</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40349</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39842</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.3501</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.55167</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46977</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42481</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41685</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.40393</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2684</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.26437</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27313</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.23845</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23396</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.18202</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.27514</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2383</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21609</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.24079</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.2724</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.26217</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28544</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.28001</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.28239</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.26999</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.21615</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.27492</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.27289</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.25743</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41388</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.42123</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24397</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39513</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38246</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41809</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.44767</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36055</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39195</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28063</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.38943</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.27366</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26534</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03975</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.24934</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24995</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.19592</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07025000000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.17772</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24407</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28458</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.26653</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.24838</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.28463</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.2677</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.37645</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46989</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.40287</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7315700000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.40789</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.45083</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40499</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30114</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27863</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37823</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38068</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34925</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28167</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.6042000000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42477</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40564</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38588</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.62078</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.78892</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.4647</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.41931</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45105</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34504</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26055</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13351</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2839100000000001</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28239</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19454</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24426</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27828</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.02275</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27955</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.11509</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.02327</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28388</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.2306</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28697</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24038</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14379</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.20875</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.21644</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.28306</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.2855</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.28955</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41472</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6190099999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5878099999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5825399999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.45425</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6000599999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.46188</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.69324</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.43803</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.44582</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.46641</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42302</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41345</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36023</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.47798</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.44975</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.44968</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.4386</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41508</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40273</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40875</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4066</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41396</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39487</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40888</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40675</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39238</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41432</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38701</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41262</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.40889</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39752</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44243</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44152</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.54003</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.48661</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44255</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42683</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.28722</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.28674</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.2383</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.2635</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.12432</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.00521</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.01555</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29489</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6734</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.26338</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.11592</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.08037999999999999</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.04877</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.25294</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.0113</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.40746</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.47185</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42107</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.49262</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.49388</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.55088</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.64966</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.64603</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.6247200000000001</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.70928</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.51552</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.50691</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.76928</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7115</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.57913</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.62326</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.40389</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.43016</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.47005</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.46749</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46194</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41475</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.51427</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41753</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.43608</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44942</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43034</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42104</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41344</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44888</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39705</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40395</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39666</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39077</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38548</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.26846</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.28711</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15351</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.26402</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03663</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40865</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45504</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41338</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46573</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.03543</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18433</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29279</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40851</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.39032</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40282</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39854</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36401</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44364</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24089</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23266</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23413</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.23424</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.00246</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13077</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.23101</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.01005</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.15978</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25614</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.00477</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14506</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15327</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.02953</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.04074000000000001</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21551</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22593</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.14895</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21094</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.26513</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28352</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2582</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.2855</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35226</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29158</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.22565</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21574</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15034</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.17891</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.05008</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01589</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00181</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04342</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.05689</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03412</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04178</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.03487</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.04495</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04872</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.03574</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.16847</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21387</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27651</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.24363</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24488</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24536</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.24975</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26257</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.28597</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27122</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26761</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25619</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.27583</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.27945</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.26429</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.27905</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26679</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27268</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.29943</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25378</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.2656</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.24984</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.23288</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.1759</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.05242</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.00495</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.06079</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.24562</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22256</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.22227</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.14012</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26828</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.25967</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24202</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.21985</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20429</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.18728</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.21131</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22454</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.16741</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.18721</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22182</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.21762</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24294</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.23027</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.21331</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.25991</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.22356</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.26718</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.26931</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.24519</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.24803</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.18199</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.06061</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.48594</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.49385</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.53999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.06806</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.22169</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.02698</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.20039</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09081</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.03959</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.0522</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.01062</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.20724</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.02895</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28972</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.00464</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02372</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.12896</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03922</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.03761</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.02714</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.07878</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.02301</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.01019</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.02467</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.04469</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23229</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.27904</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.2496</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.27742</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.17128</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32531</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.11105</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.2373</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.23946</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.24231</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.11826</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.23266</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.28825</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.11087</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25395</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14866</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.07302</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35773</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3312</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.26235</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.28715</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.26339</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.49758</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5035299999999999</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.23993</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.28523</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.28629</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.25995</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28049</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.27109</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.25533</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.13843</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.25585</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.27789</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.2541</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25711</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.28638</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.23208</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27181</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.29971</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.26508</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.26787</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41701</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.46493</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.47785</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.45904</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.47424</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.03108</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.37349</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40371</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.43474</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.47234</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.43235</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.41771</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42592</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.74563</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.45152</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40741</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45934</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40177</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36898</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46599</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.28672</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.27662</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.28647</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.18544</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.15264</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23021</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.28877</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.25377</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.17401</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.28872</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.25428</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.26235</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43122</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.40499</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.45954</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.55698</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5530900000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45796</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.54679</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49084</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39474</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.53138</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.52218</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.72793</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.76973</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5451900000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.54735</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44338</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.38836</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37568</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27328</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29111</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.27941</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.27287</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.25802</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.2576</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27378</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.20767</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.23207</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.13563</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.01942</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.13715</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.00975</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.10249</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.01386</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.04122</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02494</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23355</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.0416</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02003</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03301</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02389</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.01185</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01208</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.02799</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.11949</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06431000000000001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.12907</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.14424</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.17595</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.24254</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18843</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.15705</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.22227</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.2702</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37583</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38147</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41434</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37601</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37841</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8027799999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.27625</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.25351</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.24403</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.21462</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.21835</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.08214</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.00642</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.00383</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.00313</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03496</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.1121</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.02553</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00375</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01353</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.0449</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01331</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.02056</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15703</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.17352</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.02833</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.16125</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.13333</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.14934</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.17479</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.12382</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.21018</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.19165</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.24287</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.2225</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.26891</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.30445</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.28582</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42521</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39491</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40258</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38334</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5201399999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41127</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38794</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40331</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38678</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5190900000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39544</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25393</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.21746</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.19832</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.12741</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.17556</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.20226</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.19566</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.10203</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.12606</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.05297</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.08356999999999999</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03688</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03791</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03774</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03643</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04585</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05239</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.06797</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03543</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06179999999999999</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.08439000000000001</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.13979</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.17571</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.10196</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.20611</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.18149</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.10562</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04795</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.23532</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.11949</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.10458</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.20934</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.15648</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.17735</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.20292</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.17288</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21046</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23391</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.23491</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.25062</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.28057</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39261</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.29549</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36446</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40785</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41455</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49302</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40521</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.43071</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41101</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39241</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
